--- a/tests/fixtures/manual_spill_cache/write_child.xlsx
+++ b/tests/fixtures/manual_spill_cache/write_child.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\manual_spill_cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73D33D43-E5C0-4433-90EA-795FAD24BDA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6AEA167-2B25-4871-9ECD-3B88396054DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4545" xr2:uid="{697F8103-52CF-44CD-BAA2-48297AA7C176}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4545" xr2:uid="{C52F048C-81AA-4FF8-AF0B-62D5A0BA0EAB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -504,7 +504,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B86CA61-213A-4BE5-8114-C960558282E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D09FF3-FE82-4477-A9BE-5223B8D3CCE9}">
   <dimension ref="B2:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -525,7 +525,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B706FB68-3C77-474F-B1B7-85620A55AA45}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842F9B81-65FA-4998-8836-BAF689587ED3}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
